--- a/docs/00_기획서.xlsx
+++ b/docs/00_기획서.xlsx
@@ -107,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -129,11 +129,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -165,6 +209,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -556,6 +601,7 @@
           <t>기획서 (배경·문제·기능·스택·로드맵)</t>
         </is>
       </c>
+      <c r="C2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -565,9 +611,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -580,6 +627,7 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -592,6 +640,7 @@
           <t>오늘 날씨에 맞는 옷차림(코디)을 AI가 골라주고 네이버 쇼핑 구매로 연결하는 날씨 기반 의류 추천 웹앱</t>
         </is>
       </c>
+      <c r="C5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -604,6 +653,7 @@
           <t>✅ 완료 / 🔧 진행중 / ⬜ 예정</t>
         </is>
       </c>
+      <c r="C6" s="11" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -849,7 +899,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>보유 옷 등록(탭만으로) → 추천에 '내 옷' 반영, 부족분만 구매 추천</t>
+          <t>보유 옷 등록(탭만으로/사진 AI 인식) → 추천에 '내 옷' 반영, 부족분만 구매 추천</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -927,346 +977,363 @@
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>⑨ 사진 옷 등록</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>옷 사진을 AI(비전)가 분석해 종류·색 자동 인식 — 여러 장 동시 등록, 한 장씩 확인·수정 후 저장</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>5. 디자인 방향</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>• 모던 미니멀 / 모노크롬 블랙 — 흰 바탕 + 검정 포인트, 넉넉한 여백·라운드·소프트 섀도우. 모바일 430px 기준.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>• 색상 12팔레트(블랙/화이트/그레이/네이비/베이지/브라운/카키/블루/그린/레드/핑크/옐로우)를 옷장·추천 색칩에 공유. "AI스러운 기본 템플릿" 탈피.</t>
+          <t>• 모던 미니멀 / 모노크롬 블랙 — 흰 바탕 + 검정 포인트, 넉넉한 여백·라운드·소프트 섀도우. 모바일 430px 기준.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>• 색상 18팔레트(블랙/화이트/그레이/네이비/베이지/브라운/카키/블루/그린/레드/핑크/옐로우/와인/민트/퍼플/오렌지/아이보리/차콜)를 옷장·추천 색칩에 공유. "AI스러운 기본 템플릿" 탈피.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>6. 추천 로직</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>LLM(Claude Haiku) 우선 + 룰 기반 폴백. AI가 날씨·상황·취향·옷장에 맞춰 코디 3세트(검색어+컨셉+이유+팁+색+보유옷)를 설계 → 네이버 쇼핑으로 실제 상품 검색. 키 없거나 실패 시 체감온도 구간(TEMP_RANGE)+24절기 룰 기반으로 자동 폴백.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>LLM(Claude Haiku) 우선 + 룰 기반 폴백. AI가 날씨·상황·취향·옷장에 맞춰 코디 3세트(검색어+컨셉+이유+팁+색+보유옷)를 설계 → 네이버 쇼핑으로 실제 상품 검색. 키 없거나 실패 시 체감온도 구간(TEMP_RANGE)+24절기 룰 기반으로 자동 폴백.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>하루 범위 반영: 일 최고/최저·강수확률을 함께 전달해 '하루종일 입을 한 벌'을 설계 — 일교차 크면 레이어링, 강수확률 높으면 방수/우산 팁.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>7. 기술 스택</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>기술</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>프론트엔드</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>React 19 + Vite, 순수 CSS(모노크롬), 모바일 최적화 웹</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>백엔드</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Node 20 + Express + SQLite(better-sqlite3)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>추천 함수</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Vercel 서버리스 — /api/outfit(Claude), /api/shop(네이버 프록시)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>JWT(30일) + bcryptjs, 이메일 인증(nodemailer/Gmail SMTP)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>프론트 Vercel(weatherwear-jade.vercel.app) / 백엔드 Oracle Cloud Always Free VM(Ubuntu, AMD E2.1.Micro) + systemd + Caddy 자동 HTTPS(nip.io 도메인)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Claude API — claude-haiku-4-5, 구조화 출력(JSON 스키마)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>외부 API</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>기상청 단기예보(공공데이터, 백엔드 프록시+캐시) / 네이버 쇼핑검색 / OpenStreetMap Nominatim(역지오코딩)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>리스크: 기상청 공공 API 호출 한도·일시 장애(→ 백엔드 프록시+격자 캐시로 절감, 캐시/수동입력 폴백) / 무료 VM 1GB 저사양(스왑 2GB로 운영) / 단일 VM(자동 백업 미구축).</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>8. 로드맵</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>1. 핵심 슬라이스</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>날씨 → AI 코디 → 네이버 상품 연결</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>2. 개인화</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>옷장·찜·설정, 피부톤·핏 반영, 색상 칩</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>3. 계정·동기화</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>이메일 로그인·이메일 인증·계정별 동기화</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>4. 배포</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Vercel + Oracle VM(HTTPS)·날씨 프록시</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>5. 안정화</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>날씨 장애 폴백·추천 캐싱·하루 날씨 추천</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>6. 상용화 격차</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>비밀번호 재설정·DB 백업·개인정보처리방침/약관·모니터링</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>7. 확장</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>옷장 사진·지역별 쇼핑 API·결제/요금제</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>지역별 쇼핑 API·결제/요금제 (옷장 사진은 완료)</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>9. 나중에 추가할 기능</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>• 비밀번호 재설정(이메일) / DB 자동 백업 / 개인정보처리방침·이용약관 / 모니터링·에러추적</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>• 옷장 옷 사진 업로드 / 기존 기기 localStorage 데이터 첫 로그인 시 가져오기 / 지역별 쇼핑 API 확장 / 결제·요금제</t>
+          <t>• 비밀번호 재설정(이메일) / DB 자동 백업 / 개인정보처리방침·이용약관 / 모니터링·에러추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>• 기존 기기 localStorage 데이터 첫 로그인 시 가져오기 / 지역별 쇼핑 API 확장 / 결제·요금제</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A47:C47"/>
   <mergeCells count="25">
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="B4:C4"/>
@@ -1281,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1330,6 +1397,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>⑨ 사진 옷 등록 추가(Claude 비전 — 여러 장 동시, 한 장씩 확인 후 저장), 색 팔레트 12→18 확장, 확장 로드맵 갱신</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/00_기획서.xlsx
+++ b/docs/00_기획서.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>이메일/비밀번호 가입·로그인(JWT+bcrypt), 이메일 인증(Gmail), 미인증 차단·재전송</t>
+          <t>이메일/비밀번호 가입·로그인(JWT+bcrypt), 가입 전 인증코드 이메일 인증(6자리·10분) → 가입 즉시 로그인</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1414,6 +1414,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>가입 이메일 인증을 링크(가입 후)에서 인증코드(가입 전 확인)로 변경 — 가입 즉시 로그인</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
